--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_59_R6.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_59_R6.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7917</v>
+        <v>3.1588</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6013</v>
+        <v>3.5397</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1904</v>
+        <v>-0.3809</v>
       </c>
       <c r="G2" t="n">
         <v>-2.3508</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>2.949</v>
+        <v>1.3161</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3397</v>
+        <v>1.2781</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6093</v>
+        <v>0.038</v>
       </c>
       <c r="V2" t="n">
         <v>2.5697</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. BOSNJAKOVIC</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4009</v>
+        <v>0.1773</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7453</v>
+        <v>-0.7688</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3444</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8494</v>
+        <v>-0.8351</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.1525</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2108</v>
+        <v>-0.6826</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0336</v>
+        <v>-0.7492</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0336</v>
+        <v>0.0371</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.7863</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.883</v>
+        <v>-0.0859</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6722</v>
+        <v>-0.1896</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2108</v>
+        <v>0.1038</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5544</v>
+        <v>-0.3793</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7117</v>
+        <v>-0.0196</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1573</v>
+        <v>-0.3598</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MUURINEN</t>
+          <t>U. MIJAILOVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,19 +721,19 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0639</v>
+        <v>0.1524</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.0433</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0639</v>
+        <v>0.1091</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.168</v>
+        <v>-0.1788</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.168</v>
+        <v>-0.1788</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.168</v>
+        <v>-0.1788</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.168</v>
+        <v>-0.1788</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -766,13 +766,13 @@
         <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.0993</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.0433</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U. MIJAILOVIC</t>
+          <t>M. MUURINEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,19 +799,19 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0008</v>
+        <v>0.0639</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0755</v>
+        <v>0.0639</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1788</v>
+        <v>-0.168</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1788</v>
+        <v>-0.168</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -826,10 +826,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1788</v>
+        <v>-0.168</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1788</v>
+        <v>-0.168</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0523</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0224</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>M. BOSNJAKOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2438</v>
+        <v>-0.0709</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1227</v>
+        <v>0.2735</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8789</v>
+        <v>-0.3444</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8351</v>
+        <v>-0.8494</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1525</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6826</v>
+        <v>-0.2108</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7492</v>
+        <v>0.0336</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0371</v>
+        <v>0.0336</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0859</v>
+        <v>-0.883</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1896</v>
+        <v>-0.6722</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1038</v>
+        <v>-0.2108</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8004</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3734</v>
+        <v>0.2399</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.427</v>
+        <v>-0.1573</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4918</v>
+        <v>-0.1386</v>
       </c>
       <c r="E7" t="n">
-        <v>2.653</v>
+        <v>2.7709</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.1448</v>
+        <v>-2.9095</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1629</v>
@@ -1000,13 +1000,13 @@
         <v>3.4793</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4011</v>
+        <v>-0.0479</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3189</v>
+        <v>0.4369</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.72</v>
+        <v>-0.4848</v>
       </c>
       <c r="V7" t="n">
         <v>1.0722</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9605</v>
+        <v>-2.3049</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7198</v>
+        <v>-0.3406</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2407</v>
+        <v>-1.9643</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0339</v>
+        <v>-4.6366</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2245</v>
+        <v>-0.4274</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2584</v>
+        <v>-4.2092</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2398</v>
+        <v>-1.1736</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1294</v>
+        <v>0.1414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1104</v>
+        <v>-1.3151</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.2738</v>
+        <v>-3.463</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9049</v>
+        <v>-0.5688</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.3688</v>
+        <v>-2.8942</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2511</v>
+        <v>0.579</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8417</v>
+        <v>0.472</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4094</v>
+        <v>0.107</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.6805</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.6805</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9847</v>
+        <v>-2.3309</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0132</v>
+        <v>-0.9558</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9979</v>
+        <v>-1.3751</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.6366</v>
+        <v>-2.0339</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4274</v>
+        <v>0.2245</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.2092</v>
+        <v>-2.2584</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1736</v>
+        <v>1.2398</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1414</v>
+        <v>1.1294</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3151</v>
+        <v>0.1104</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.463</v>
+        <v>-3.2738</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5688</v>
+        <v>-0.9049</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.8942</v>
+        <v>-2.3688</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9278</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8992</v>
+        <v>0.8808</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8259</v>
+        <v>0.6058</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.275</v>
       </c>
       <c r="V9" t="n">
-        <v>2.6805</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>2.6805</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6486</v>
+        <v>-3.1224</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0549</v>
+        <v>-1.7315</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5938</v>
+        <v>-1.3909</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.952</v>
+        <v>-3.8616</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0143</v>
+        <v>-1.6266</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9377</v>
+        <v>-2.2351</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5716</v>
+        <v>-2.007</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8907</v>
+        <v>-1.4046</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4623</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3804</v>
+        <v>-1.8547</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9049</v>
+        <v>-0.222</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4755</v>
+        <v>-1.6327</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.9432</v>
+        <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3356</v>
+        <v>-0.5081</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6765</v>
+        <v>0.2754</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0121</v>
+        <v>-0.7835</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3247</v>
+        <v>-3.1876</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9674</v>
+        <v>-1.5267</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3573</v>
+        <v>-1.661</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8616</v>
+        <v>-2.952</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6266</v>
+        <v>-0.0143</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2351</v>
+        <v>-2.9377</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.007</v>
+        <v>-0.5716</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4046</v>
+        <v>0.8907</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-1.4623</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8547</v>
+        <v>-2.3804</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.222</v>
+        <v>-0.9049</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6327</v>
+        <v>-1.4755</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3195</v>
+        <v>2.7834</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3195</v>
+        <v>3.9432</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7103</v>
+        <v>-0.8746</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0395</v>
+        <v>0.2047</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7499</v>
+        <v>-1.0794</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9597</v>
+        <v>-4.8481</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7278</v>
+        <v>-1.7842</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2319</v>
+        <v>-3.0639</v>
       </c>
       <c r="G12" t="n">
         <v>-6.5568</v>
@@ -1390,13 +1390,13 @@
         <v>3.4793</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9518</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.955</v>
+        <v>-0.0114</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9968</v>
+        <v>-0.8287</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9304</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.615</v>
+        <v>-5.5205</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3706</v>
+        <v>-4.545</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2444</v>
+        <v>-0.9755</v>
       </c>
       <c r="G13" t="n">
         <v>-4.1305</v>
@@ -1468,13 +1468,13 @@
         <v>2.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.165</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3181</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.847</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
@@ -1504,10 +1504,10 @@
         <v>-17.9715</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.025099999999999</v>
+        <v>-5.0252</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.9465</v>
+        <v>-12.9464</v>
       </c>
       <c r="G14" t="n">
         <v>-29.7164</v>
@@ -1546,7 +1546,7 @@
         <v>24.3551</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2372000000000001</v>
+        <v>0.2372</v>
       </c>
       <c r="T14" t="n">
         <v>4.0327</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9424</v>
+        <v>7.1682</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0665</v>
+        <v>4.5383</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8759</v>
+        <v>2.6299</v>
       </c>
       <c r="G15" t="n">
         <v>8.9114</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1907</v>
+        <v>0.4165</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3655</v>
+        <v>0.1063</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5562</v>
+        <v>0.3102</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6022</v>
+        <v>6.433</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9122</v>
+        <v>3.384</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6901</v>
+        <v>3.049</v>
       </c>
       <c r="G16" t="n">
         <v>5.8061</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6677</v>
+        <v>0.163</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2908</v>
+        <v>0.181</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3769</v>
+        <v>-0.018</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4861</v>
+        <v>4.334</v>
       </c>
       <c r="E17" t="n">
-        <v>5.4101</v>
+        <v>5.9999</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.924</v>
+        <v>-1.6659</v>
       </c>
       <c r="G17" t="n">
         <v>4.5069</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3403</v>
+        <v>-0.4925</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3655</v>
+        <v>0.2243</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9748</v>
+        <v>-0.7167</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3024</v>
+        <v>2.8225</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0063</v>
+        <v>4.2752</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2961</v>
+        <v>-1.4527</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9328</v>
+        <v>3.9026</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1259</v>
+        <v>1.306</v>
       </c>
       <c r="I18" t="n">
-        <v>1.807</v>
+        <v>2.5966</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5642</v>
+        <v>5.0141</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3802</v>
+        <v>1.8856</v>
       </c>
       <c r="L18" t="n">
-        <v>0.184</v>
+        <v>3.1284</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3686</v>
+        <v>-1.1115</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2543</v>
+        <v>-0.5796</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6229</v>
+        <v>-0.5319</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>2.117</v>
+        <v>-0.2399</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9935</v>
+        <v>0.4208</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1235</v>
+        <v>-0.6607</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5308</v>
+        <v>2.45</v>
       </c>
       <c r="E19" t="n">
-        <v>4.2752</v>
+        <v>1.0646</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7444</v>
+        <v>1.3855</v>
       </c>
       <c r="G19" t="n">
-        <v>3.9026</v>
+        <v>2.0619</v>
       </c>
       <c r="H19" t="n">
-        <v>1.306</v>
+        <v>0.1982</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5966</v>
+        <v>1.8637</v>
       </c>
       <c r="J19" t="n">
-        <v>5.0141</v>
+        <v>1.3722</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8856</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>3.1284</v>
+        <v>1.2882</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1115</v>
+        <v>0.6897</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5796</v>
+        <v>0.1141</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5319</v>
+        <v>0.5756</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5316</v>
+        <v>0.3881</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4208</v>
+        <v>0.0119</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9524</v>
+        <v>0.3763</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2477</v>
+        <v>2.2269</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8287</v>
+        <v>2.2902</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4191</v>
+        <v>-0.0633</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0619</v>
+        <v>3.8822</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1982</v>
+        <v>0.7971</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8637</v>
+        <v>3.0851</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3722</v>
+        <v>2.4277</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08400000000000001</v>
+        <v>1.1763</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2882</v>
+        <v>1.2514</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6897</v>
+        <v>1.4545</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1141</v>
+        <v>-0.3792</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5756</v>
+        <v>1.8337</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1858</v>
+        <v>-0.297</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.224</v>
+        <v>0.0944</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4099</v>
+        <v>-0.3914</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6321</v>
+        <v>1.8369</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0543</v>
+        <v>-1.2912</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4223</v>
+        <v>3.128</v>
       </c>
       <c r="G21" t="n">
-        <v>3.8822</v>
+        <v>1.9328</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7971</v>
+        <v>0.1259</v>
       </c>
       <c r="I21" t="n">
-        <v>3.0851</v>
+        <v>1.807</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4277</v>
+        <v>0.5642</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1763</v>
+        <v>0.3802</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2514</v>
+        <v>0.184</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4545</v>
+        <v>1.3686</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3792</v>
+        <v>-0.2543</v>
       </c>
       <c r="O21" t="n">
-        <v>1.8337</v>
+        <v>1.6229</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8918</v>
+        <v>0.6515</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1415</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7503</v>
+        <v>-0.0446</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2862</v>
+        <v>-0.2836</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2862</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5251</v>
+        <v>0.6572</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8753</v>
+        <v>2.0885</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3502</v>
+        <v>-1.4314</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6849</v>
+        <v>-0.848</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4632</v>
+        <v>-0.7743</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1481</v>
+        <v>-0.0737</v>
       </c>
       <c r="J22" t="n">
-        <v>2.55</v>
+        <v>0.8925</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.1947</v>
       </c>
       <c r="L22" t="n">
-        <v>2.4659</v>
+        <v>1.0872</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8651</v>
+        <v>-1.7405</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5473</v>
+        <v>-0.5796</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3178</v>
+        <v>-1.1609</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.232</v>
+        <v>-0.4099</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6449</v>
+        <v>0.2989</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4129</v>
+        <v>-0.7088</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3.0748</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3251</v>
+        <v>0.4465</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4988</v>
+        <v>0.6394</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8239</v>
+        <v>-0.1929</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.848</v>
+        <v>1.6849</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7743</v>
+        <v>-0.4632</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0737</v>
+        <v>2.1481</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8925</v>
+        <v>2.55</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1947</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>1.0872</v>
+        <v>2.4659</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7405</v>
+        <v>-0.8651</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5796</v>
+        <v>-0.5473</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1609</v>
+        <v>-0.3178</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3921</v>
+        <v>0.1533</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2908</v>
+        <v>0.409</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1013</v>
+        <v>-0.2557</v>
       </c>
       <c r="V23" t="n">
-        <v>3.0748</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5955</v>
+        <v>-1.1281</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6909</v>
+        <v>-1.0447</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0954</v>
+        <v>-0.0834</v>
       </c>
       <c r="G24" t="n">
         <v>0.588</v>
@@ -2326,13 +2326,13 @@
         <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9041</v>
+        <v>0.3714</v>
       </c>
       <c r="T24" t="n">
-        <v>0.637</v>
+        <v>0.2831</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2671</v>
+        <v>0.0883</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.0071</v>
+        <v>-2.6317</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7922</v>
+        <v>-4.9102</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7851</v>
+        <v>2.2784</v>
       </c>
       <c r="G25" t="n">
         <v>-0.3756</v>
@@ -2404,13 +2404,13 @@
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.3675</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4955</v>
+        <v>0.3776</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5034</v>
+        <v>-0.0101</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5361</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3695</v>
+        <v>-5.0709</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4256</v>
+        <v>-3.0154</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.9439</v>
+        <v>-2.0555</v>
       </c>
       <c r="G26" t="n">
         <v>-2.3368</v>
@@ -2482,13 +2482,13 @@
         <v>1.1598</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9647</v>
+        <v>0.2634</v>
       </c>
       <c r="T26" t="n">
-        <v>1.2819</v>
+        <v>0.6921</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3172</v>
+        <v>-0.4288</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6778999999999999</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>17.9716</v>
+        <v>19.5445</v>
       </c>
       <c r="E27" t="n">
-        <v>14.0187</v>
+        <v>14.0186</v>
       </c>
       <c r="F27" t="n">
-        <v>3.953</v>
+        <v>5.525700000000001</v>
       </c>
       <c r="G27" t="n">
         <v>29.7164</v>
@@ -2530,13 +2530,13 @@
         <v>4.772</v>
       </c>
       <c r="I27" t="n">
-        <v>24.9445</v>
+        <v>24.94449999999999</v>
       </c>
       <c r="J27" t="n">
         <v>29.217</v>
       </c>
       <c r="K27" t="n">
-        <v>8.155100000000001</v>
+        <v>8.155099999999999</v>
       </c>
       <c r="L27" t="n">
         <v>21.0617</v>
@@ -2548,7 +2548,7 @@
         <v>-3.3832</v>
       </c>
       <c r="O27" t="n">
-        <v>3.882700000000001</v>
+        <v>3.8827</v>
       </c>
       <c r="P27" t="n">
         <v>-8.118399999999999</v>
@@ -2560,13 +2560,13 @@
         <v>16.2368</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2370999999999998</v>
+        <v>1.3354</v>
       </c>
       <c r="T27" t="n">
-        <v>3.795500000000001</v>
+        <v>3.7955</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.0325</v>
+        <v>-2.46</v>
       </c>
       <c r="V27" t="n">
         <v>-3.3895</v>
